--- a/data/trans_dic/P24D-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,23; 51,61</t>
+          <t>35,79; 52,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,68; 64,85</t>
+          <t>46,99; 63,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,71; 66,08</t>
+          <t>45,86; 66,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,94; 55,25</t>
+          <t>33,27; 55,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 48,58</t>
+          <t>28,25; 49,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,96; 63,4</t>
+          <t>42,72; 62,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,96; 66,27</t>
+          <t>42,78; 65,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,35; 58,8</t>
+          <t>38,99; 58,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,06; 47,65</t>
+          <t>35,39; 48,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,83; 60,76</t>
+          <t>48,12; 60,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,71; 64,14</t>
+          <t>47,15; 63,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,95; 53,81</t>
+          <t>39,24; 54,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,11; 42,02</t>
+          <t>24,7; 41,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,75; 61,79</t>
+          <t>44,62; 61,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,61; 60,94</t>
+          <t>38,84; 59,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,92; 49,54</t>
+          <t>28,24; 49,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 46,01</t>
+          <t>28,35; 45,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,42; 70,8</t>
+          <t>49,84; 69,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,48; 53,62</t>
+          <t>33,23; 52,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,55; 51,73</t>
+          <t>33,01; 51,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 41,11</t>
+          <t>28,39; 40,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,61; 62,98</t>
+          <t>50,12; 62,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39,79; 53,46</t>
+          <t>38,57; 53,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,64; 47,8</t>
+          <t>33,75; 47,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 38,69</t>
+          <t>25,88; 37,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,9; 57,68</t>
+          <t>45,68; 58,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,02; 52,69</t>
+          <t>39,08; 53,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,04; 43,73</t>
+          <t>24,27; 43,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 51,94</t>
+          <t>21,52; 51,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,09; 56,22</t>
+          <t>33,94; 55,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,37; 66,21</t>
+          <t>38,92; 66,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,08; 62,79</t>
+          <t>30,35; 61,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,64; 38,28</t>
+          <t>27,44; 38,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,54; 55,01</t>
+          <t>44,17; 55,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,93; 53,35</t>
+          <t>41,76; 53,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,15; 44,6</t>
+          <t>27,22; 43,08</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,04; 34,68</t>
+          <t>26,85; 34,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,39; 51,42</t>
+          <t>41,9; 51,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,89; 47,71</t>
+          <t>38,49; 47,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 44,03</t>
+          <t>31,21; 44,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,07; 42,44</t>
+          <t>29,96; 42,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,24; 59,63</t>
+          <t>47,45; 60,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,37; 51,48</t>
+          <t>40,5; 51,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,48; 52,77</t>
+          <t>40,33; 52,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,98; 35,8</t>
+          <t>28,43; 35,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,61; 52,77</t>
+          <t>45,57; 52,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,73; 47,93</t>
+          <t>40,71; 48,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,25; 45,53</t>
+          <t>36,39; 44,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,58; 33,67</t>
+          <t>21,1; 34,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,54; 42,56</t>
+          <t>29,65; 42,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,21; 43,13</t>
+          <t>30,59; 42,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,76; 38,03</t>
+          <t>22,43; 38,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 41,4</t>
+          <t>25,98; 41,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,53; 59,41</t>
+          <t>45,01; 59,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,91; 51,46</t>
+          <t>38,02; 51,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,31; 48,89</t>
+          <t>34,63; 48,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,48; 35,3</t>
+          <t>25,42; 35,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,86; 49,03</t>
+          <t>38,57; 48,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,78; 44,91</t>
+          <t>35,69; 45,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,71; 41,06</t>
+          <t>30,37; 41,25</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,78</t>
+          <t>2,75; 12,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 29,54</t>
+          <t>11,0; 31,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,55; 39,8</t>
+          <t>18,0; 37,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,82</t>
+          <t>0,0; 47,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,96; 38,71</t>
+          <t>25,42; 39,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,44; 49,37</t>
+          <t>32,84; 48,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,49; 43,04</t>
+          <t>27,52; 43,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,3; 49,5</t>
+          <t>29,21; 51,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,29; 28,92</t>
+          <t>17,94; 29,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,75; 41,66</t>
+          <t>29,03; 41,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,06; 40,19</t>
+          <t>26,66; 39,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,14; 41,65</t>
+          <t>23,45; 42,04</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,76; 33,01</t>
+          <t>27,8; 33,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,37; 49,14</t>
+          <t>43,61; 49,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,09; 46,0</t>
+          <t>40,13; 46,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,87</t>
+          <t>31,63; 39,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,67; 38,4</t>
+          <t>31,73; 38,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,24; 54,8</t>
+          <t>48,02; 54,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,95; 47,67</t>
+          <t>41,21; 47,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,59; 47,31</t>
+          <t>40,44; 47,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,17; 34,3</t>
+          <t>30,27; 34,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,19; 50,68</t>
+          <t>46,46; 50,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,39; 45,85</t>
+          <t>41,32; 45,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,46; 41,83</t>
+          <t>36,38; 42,14</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54397; 77502</t>
+          <t>53742; 78207</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70718; 96176</t>
+          <t>69684; 94025</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49666; 70254</t>
+          <t>48762; 70190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27964; 46900</t>
+          <t>28244; 47042</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25282; 43816</t>
+          <t>25478; 44705</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41486; 62685</t>
+          <t>42241; 61592</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27228; 44056</t>
+          <t>28440; 43587</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26047; 39935</t>
+          <t>26479; 39861</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84262; 114524</t>
+          <t>85065; 115820</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118226; 150192</t>
+          <t>118950; 150396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82440; 110831</t>
+          <t>81481; 109560</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59515; 82223</t>
+          <t>59960; 82580</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32588; 56800</t>
+          <t>33393; 55758</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65834; 92978</t>
+          <t>67142; 93136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42480; 63740</t>
+          <t>40622; 62475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25885; 45928</t>
+          <t>26187; 45802</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37926; 60697</t>
+          <t>37407; 59850</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63654; 87639</t>
+          <t>61700; 85898</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32498; 53652</t>
+          <t>33250; 52504</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27152; 43147</t>
+          <t>27533; 43176</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76210; 109798</t>
+          <t>75840; 107921</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138818; 172718</t>
+          <t>137457; 172618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81424; 109400</t>
+          <t>78930; 108928</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59252; 84185</t>
+          <t>59444; 83936</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67725; 98264</t>
+          <t>65735; 96373</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122102; 156858</t>
+          <t>124221; 158030</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84573; 114196</t>
+          <t>84709; 115284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28865; 52500</t>
+          <t>29144; 51720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10238; 22911</t>
+          <t>9492; 22678</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29061; 47923</t>
+          <t>28934; 46916</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20143; 34764</t>
+          <t>20432; 34759</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8177; 16007</t>
+          <t>7738; 15754</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82398; 114100</t>
+          <t>81780; 114795</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>159104; 196474</t>
+          <t>157780; 197592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110202; 143627</t>
+          <t>112441; 144387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40967; 64913</t>
+          <t>39625; 62700</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>152187; 195135</t>
+          <t>151116; 194442</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>211679; 256799</t>
+          <t>209232; 257812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163011; 205249</t>
+          <t>165599; 204980</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102119; 149045</t>
+          <t>105656; 150912</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72036; 101670</t>
+          <t>71767; 100679</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>132611; 167374</t>
+          <t>133200; 169426</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>127505; 162590</t>
+          <t>127901; 162632</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86263; 112433</t>
+          <t>85936; 111303</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>232470; 287227</t>
+          <t>228089; 283784</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>355815; 411624</t>
+          <t>355510; 413251</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>303828; 357541</t>
+          <t>303695; 358637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>199930; 251125</t>
+          <t>200705; 247959</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38617; 63166</t>
+          <t>39579; 63842</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64176; 92450</t>
+          <t>64403; 91694</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72864; 104030</t>
+          <t>73798; 103449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33758; 58982</t>
+          <t>34790; 59672</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47474; 73890</t>
+          <t>46357; 73864</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95933; 127999</t>
+          <t>96981; 128970</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81544; 110683</t>
+          <t>81776; 111270</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55730; 77164</t>
+          <t>54654; 77203</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93268; 129217</t>
+          <t>93058; 130260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168148; 212123</t>
+          <t>166894; 210309</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>163249; 204935</t>
+          <t>162839; 207007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96105; 128503</t>
+          <t>95057; 129096</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1930; 11211</t>
+          <t>2414; 11241</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6880; 18479</t>
+          <t>6884; 19403</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12630; 28637</t>
+          <t>12954; 27268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 9940</t>
+          <t>0; 11805</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42229; 65484</t>
+          <t>43003; 66310</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54903; 81067</t>
+          <t>53913; 80344</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49013; 74050</t>
+          <t>47349; 74570</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23976; 41941</t>
+          <t>24749; 43513</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46972; 74281</t>
+          <t>46073; 74549</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65188; 94463</t>
+          <t>65828; 94492</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66013; 98063</t>
+          <t>65043; 95770</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25377; 45683</t>
+          <t>25727; 46116</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>382408; 454732</t>
+          <t>382918; 456890</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>585448; 663346</t>
+          <t>588633; 667283</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>469450; 538698</t>
+          <t>469887; 538652</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>255846; 317254</t>
+          <t>258159; 323453</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>270244; 327726</t>
+          <t>270813; 324764</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>467081; 530613</t>
+          <t>464976; 528909</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>377594; 439527</t>
+          <t>379914; 442177</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>256705; 299220</t>
+          <t>255736; 298698</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>673058; 765056</t>
+          <t>675327; 765894</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1070713; 1174922</t>
+          <t>1077109; 1173542</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>866329; 959633</t>
+          <t>864810; 956682</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>528142; 606023</t>
+          <t>527091; 610469</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P24D-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,79; 52,08</t>
+          <t>35,87; 51,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,99; 63,4</t>
+          <t>46,25; 63,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,86; 66,01</t>
+          <t>46,33; 67,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,27; 55,41</t>
+          <t>35,39; 57,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,25; 49,57</t>
+          <t>28,12; 47,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,72; 62,29</t>
+          <t>42,56; 62,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,78; 65,56</t>
+          <t>42,12; 66,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,99; 58,69</t>
+          <t>38,95; 57,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,39; 48,19</t>
+          <t>35,21; 48,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,12; 60,84</t>
+          <t>48,08; 60,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47,15; 63,4</t>
+          <t>46,96; 62,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,24; 54,04</t>
+          <t>39,94; 54,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,7; 41,25</t>
+          <t>23,4; 40,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,62; 61,89</t>
+          <t>43,74; 61,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,84; 59,73</t>
+          <t>38,96; 59,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,24; 49,4</t>
+          <t>30,03; 51,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,35; 45,37</t>
+          <t>28,04; 44,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,84; 69,39</t>
+          <t>50,98; 70,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,23; 52,47</t>
+          <t>32,98; 52,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,01; 51,77</t>
+          <t>34,21; 52,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,39; 40,41</t>
+          <t>28,33; 40,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,12; 62,94</t>
+          <t>50,08; 63,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,57; 53,23</t>
+          <t>39,07; 53,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,75; 47,66</t>
+          <t>34,6; 49,07</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,88; 37,95</t>
+          <t>26,33; 38,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,68; 58,11</t>
+          <t>45,1; 57,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,08; 53,19</t>
+          <t>38,81; 52,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,27; 43,08</t>
+          <t>25,17; 43,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,52; 51,42</t>
+          <t>22,64; 49,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,94; 55,03</t>
+          <t>33,44; 55,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,92; 66,2</t>
+          <t>38,29; 65,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,35; 61,8</t>
+          <t>31,36; 61,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,44; 38,51</t>
+          <t>27,27; 37,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,17; 55,32</t>
+          <t>43,84; 55,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,76; 53,63</t>
+          <t>40,59; 53,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27,22; 43,08</t>
+          <t>28,01; 44,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,85; 34,55</t>
+          <t>26,35; 34,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,9; 51,63</t>
+          <t>41,93; 51,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,49; 47,65</t>
+          <t>37,97; 47,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,21; 44,59</t>
+          <t>30,73; 42,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,96; 42,03</t>
+          <t>30,32; 42,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,45; 60,36</t>
+          <t>47,12; 59,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,5; 51,5</t>
+          <t>40,38; 51,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,33; 52,24</t>
+          <t>41,05; 53,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,43; 35,37</t>
+          <t>28,99; 35,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,57; 52,97</t>
+          <t>45,75; 52,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,71; 48,07</t>
+          <t>40,72; 48,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,39; 44,96</t>
+          <t>36,63; 45,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,1; 34,03</t>
+          <t>20,73; 33,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,65; 42,21</t>
+          <t>29,52; 42,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,59; 42,89</t>
+          <t>30,56; 42,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,43; 38,47</t>
+          <t>24,2; 40,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,98; 41,39</t>
+          <t>26,33; 40,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,01; 59,86</t>
+          <t>44,9; 59,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,02; 51,73</t>
+          <t>38,21; 51,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,63; 48,91</t>
+          <t>35,51; 48,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,58</t>
+          <t>25,09; 35,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,57; 48,61</t>
+          <t>38,9; 48,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,69; 45,36</t>
+          <t>35,91; 44,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,37; 41,25</t>
+          <t>32,31; 42,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,82</t>
+          <t>2,3; 13,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 31,02</t>
+          <t>12,26; 31,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,0; 37,9</t>
+          <t>18,13; 39,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,29</t>
+          <t>0,0; 37,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,42; 39,2</t>
+          <t>25,09; 39,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,84; 48,93</t>
+          <t>33,54; 48,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,52; 43,35</t>
+          <t>28,05; 43,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,21; 51,36</t>
+          <t>29,45; 49,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,94; 29,02</t>
+          <t>18,5; 28,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,03; 41,67</t>
+          <t>29,11; 41,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,66; 39,25</t>
+          <t>26,64; 39,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,45; 42,04</t>
+          <t>23,88; 42,27</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,8; 33,17</t>
+          <t>28,04; 33,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,61; 49,43</t>
+          <t>43,55; 49,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,13; 46,0</t>
+          <t>40,1; 45,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,63; 39,63</t>
+          <t>32,24; 39,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,73; 38,06</t>
+          <t>31,48; 38,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,02; 54,62</t>
+          <t>47,62; 54,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,21; 47,96</t>
+          <t>41,41; 47,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,44; 47,23</t>
+          <t>40,78; 47,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,27; 34,33</t>
+          <t>30,18; 34,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,46; 50,62</t>
+          <t>46,21; 50,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41,32; 45,71</t>
+          <t>41,54; 46,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,38; 42,14</t>
+          <t>36,94; 42,01</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70739</t>
+          <t>78454</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53742; 78207</t>
+          <t>53862; 77596</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69684; 94025</t>
+          <t>68595; 94268</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48762; 70190</t>
+          <t>49260; 71270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28244; 47042</t>
+          <t>33367; 53908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25478; 44705</t>
+          <t>25358; 43271</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42241; 61592</t>
+          <t>42082; 62283</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28440; 43587</t>
+          <t>28004; 44416</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26479; 39861</t>
+          <t>27981; 41433</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85065; 115820</t>
+          <t>84623; 115972</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118950; 150396</t>
+          <t>118841; 150720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81481; 109560</t>
+          <t>81147; 108001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59960; 82580</t>
+          <t>66353; 90749</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35507</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>77213</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33393; 55758</t>
+          <t>31623; 55409</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67142; 93136</t>
+          <t>65814; 93281</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40622; 62475</t>
+          <t>40747; 62439</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26187; 45802</t>
+          <t>28465; 49288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37407; 59850</t>
+          <t>36990; 58555</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61700; 85898</t>
+          <t>63108; 87142</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33250; 52504</t>
+          <t>33000; 52684</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27533; 43176</t>
+          <t>31646; 48383</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>75840; 107921</t>
+          <t>75656; 107044</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>137457; 172618</t>
+          <t>137344; 173688</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78930; 108928</t>
+          <t>79950; 108924</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59444; 83936</t>
+          <t>64801; 91920</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39833</t>
+          <t>42756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51751</t>
+          <t>55303</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65735; 96373</t>
+          <t>66875; 96982</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>124221; 158030</t>
+          <t>122640; 156383</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84709; 115284</t>
+          <t>84110; 114422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29144; 51720</t>
+          <t>32125; 55996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9492; 22678</t>
+          <t>9984; 22028</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28934; 46916</t>
+          <t>28507; 47186</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20432; 34759</t>
+          <t>20104; 34190</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7738; 15754</t>
+          <t>8571; 16881</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81780; 114795</t>
+          <t>81298; 112893</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157780; 197592</t>
+          <t>156605; 196696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112441; 144387</t>
+          <t>109294; 144674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39625; 62700</t>
+          <t>43398; 68822</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126232</t>
+          <t>132545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>108747</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>225435</t>
+          <t>241292</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151116; 194442</t>
+          <t>148253; 193492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>209232; 257812</t>
+          <t>209382; 255684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165599; 204980</t>
+          <t>163328; 205250</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105656; 150912</t>
+          <t>111656; 153797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71767; 100679</t>
+          <t>72626; 101491</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>133200; 169426</t>
+          <t>132270; 168045</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>127901; 162632</t>
+          <t>127539; 163934</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85936; 111303</t>
+          <t>94643; 122931</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>228089; 283784</t>
+          <t>232617; 284898</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>355510; 413251</t>
+          <t>356915; 413175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>303695; 358637</t>
+          <t>303743; 360830</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>200705; 247959</t>
+          <t>217535; 267858</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46072</t>
+          <t>57735</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65942</t>
+          <t>72374</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>112015</t>
+          <t>130109</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39579; 63842</t>
+          <t>38892; 62797</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64403; 91694</t>
+          <t>64115; 91805</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73798; 103449</t>
+          <t>73710; 103288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34790; 59672</t>
+          <t>43495; 71909</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>46357; 73864</t>
+          <t>46987; 73004</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96981; 128970</t>
+          <t>96738; 127815</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81776; 111270</t>
+          <t>82181; 111316</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54654; 77203</t>
+          <t>61320; 84530</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93058; 130260</t>
+          <t>91841; 128708</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166894; 210309</t>
+          <t>168318; 211258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162839; 207007</t>
+          <t>163847; 204607</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95057; 129096</t>
+          <t>113873; 149753</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>36499</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2414; 11241</t>
+          <t>2019; 11523</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6884; 19403</t>
+          <t>7668; 19860</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12954; 27268</t>
+          <t>13044; 28103</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 11805</t>
+          <t>0; 8710</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43003; 66310</t>
+          <t>42440; 66897</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53913; 80344</t>
+          <t>55063; 79938</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47349; 74570</t>
+          <t>48246; 75511</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24749; 43513</t>
+          <t>26553; 44989</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46073; 74549</t>
+          <t>47519; 73569</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65828; 94492</t>
+          <t>66014; 94005</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65043; 95770</t>
+          <t>64988; 95501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25727; 46116</t>
+          <t>27128; 48026</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287333</t>
+          <t>315851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>278840</t>
+          <t>303017</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>566174</t>
+          <t>618868</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>382918; 456890</t>
+          <t>386262; 455803</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>588633; 667283</t>
+          <t>587898; 670505</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>469887; 538652</t>
+          <t>469630; 537788</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>258159; 323453</t>
+          <t>284750; 350504</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>270813; 324764</t>
+          <t>268655; 325686</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>464976; 528909</t>
+          <t>461093; 527618</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>379914; 442177</t>
+          <t>381797; 441009</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>255736; 298698</t>
+          <t>279424; 328341</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>675327; 765894</t>
+          <t>673341; 763968</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1077109; 1173542</t>
+          <t>1071267; 1173467</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>864810; 956682</t>
+          <t>869421; 962778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>527091; 610469</t>
+          <t>579362; 658822</t>
         </is>
       </c>
     </row>
